--- a/public/exel/Form2.xlsx
+++ b/public/exel/Form2.xlsx
@@ -1,29 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\sbfp_ao_system\public\exel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF5DCB6-16DF-411F-B8D4-0ADDD3FC6039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603119F3-E021-4C28-AA96-31D316E0EC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SBFP-FORM 2" sheetId="3" r:id="rId1"/>
+    <sheet name="SBFP-FORM 2 START (2)" sheetId="10" r:id="rId1"/>
     <sheet name="SBFP-FORM 5" sheetId="7" state="hidden" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'SBFP-FORM 2'!$12:$13</definedName>
-  </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,24 +25,31 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId12" roundtripDataChecksum="i4YdossULAAQ9Ob2UTVIl3MUynszPQ4ybfP3n2JY/lI="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId14" roundtripDataChecksum="Q3mEZv6mcSlL5WM+Jlsqx8yaIgS+xr9nhVFW54jWbJU="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="81">
   <si>
     <t>Department of Education</t>
   </si>
   <si>
-    <t>Sex</t>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Stunted</t>
+  </si>
+  <si>
+    <t>Wasted</t>
+  </si>
+  <si>
+    <t>Prepared by:</t>
   </si>
   <si>
     <t>Approved by:</t>
@@ -57,18 +58,9 @@
     <t>School Head</t>
   </si>
   <si>
-    <t>SBFP Form 2 (2024)</t>
-  </si>
-  <si>
-    <t>Date of Start of Feeding:  __________________________</t>
-  </si>
-  <si>
     <t>Number of Undernourished School Children by Grade Level</t>
   </si>
   <si>
-    <t>Nutritional Status at Start/End of Feeding</t>
-  </si>
-  <si>
     <t>No. of Secondary Targets</t>
   </si>
   <si>
@@ -79,19 +71,10 @@
   </si>
   <si>
     <t>No. of Pupils who are beneficiaries in previous years (Repeaters)</t>
-  </si>
-  <si>
-    <t>Date Feeding Started/Ended</t>
   </si>
   <si>
     <t>Severely
 Wasted</t>
-  </si>
-  <si>
-    <t>Wasted</t>
-  </si>
-  <si>
-    <t>Normal</t>
   </si>
   <si>
     <t>Overweight
@@ -103,9 +86,6 @@
 Stunted</t>
   </si>
   <si>
-    <t>Stunted</t>
-  </si>
-  <si>
     <t>Tall</t>
   </si>
   <si>
@@ -124,48 +104,39 @@
     <t>1.  Kinder</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>F</t>
+    <t>2.  Grade I</t>
+  </si>
+  <si>
+    <t>3.  Grade II</t>
+  </si>
+  <si>
+    <t>4.  Grade III</t>
+  </si>
+  <si>
+    <t>5. Grade IV</t>
+  </si>
+  <si>
+    <t>6.  Grade V</t>
+  </si>
+  <si>
+    <t>7.  Grade VI</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
-    <t>2.  Grade I</t>
-  </si>
-  <si>
-    <t>3.  Grade II</t>
-  </si>
-  <si>
-    <t>4.  Grade III</t>
-  </si>
-  <si>
-    <t>5. Grade IV</t>
-  </si>
-  <si>
-    <t>6.  Grade V</t>
-  </si>
-  <si>
-    <t>7.  Grade VI</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Prepared by:</t>
-  </si>
-  <si>
     <t>Note:  This form shall be prepared by the school before the start of feeding and after feeding, to be compiled by the SDO, and for final compilation by the RO, for submission to  DepEd BLSS-SHD</t>
   </si>
   <si>
+    <t>AVERAGE:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBFP Form 5 </t>
+  </si>
+  <si>
     <t>SCHOOL-BASED FEEDING PROGRAM</t>
   </si>
   <si>
-    <t xml:space="preserve">SBFP Form 5 </t>
-  </si>
-  <si>
     <t>CONSOLIDATED NUTRITIONAL STATUS AND ATTENDANCE REPORT</t>
   </si>
   <si>
@@ -218,9 +189,6 @@
   </si>
   <si>
     <t>TOTAL</t>
-  </si>
-  <si>
-    <t>AVERAGE:</t>
   </si>
   <si>
     <t>Legend:</t>
@@ -238,6 +206,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>SW</t>
     </r>
@@ -246,6 +215,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> - Severely Wasted</t>
     </r>
@@ -257,6 +227,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>SU</t>
     </r>
@@ -265,6 +236,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> - Severely Underw</t>
     </r>
@@ -273,6 +245,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>eight</t>
     </r>
@@ -284,6 +257,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>W</t>
     </r>
@@ -292,6 +266,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> - Wasted</t>
     </r>
@@ -303,6 +278,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>U</t>
     </r>
@@ -311,6 +287,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> - Underw</t>
     </r>
@@ -319,6 +296,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>eight</t>
     </r>
@@ -330,6 +308,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>N</t>
     </r>
@@ -338,6 +317,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> - Normal</t>
     </r>
@@ -349,6 +329,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">N </t>
     </r>
@@ -357,6 +338,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>- Normal</t>
     </r>
@@ -368,6 +350,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>Ow</t>
     </r>
@@ -376,6 +359,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> - Overweight</t>
     </r>
@@ -387,6 +371,28 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - Overweight</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>O</t>
     </r>
@@ -395,6 +401,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> - Obese</t>
     </r>
@@ -415,187 +422,76 @@
     <t>Note:  This form shall be prepared by the school using the data from SBFP Form 4.</t>
   </si>
   <si>
-    <t>City/ Municipality/Barangay : MALAYBALAY CITY/BUKIDNON/MANAGOK</t>
-  </si>
-  <si>
-    <t>SCHOOL-BASED FEEDING PROGRAM (SBFP) SUMMARY OF BENEFICIARIES &amp; START OF FEEDING (SY: 2025-2026)</t>
-  </si>
-  <si>
-    <t>Schools Division Office: MALAYBALAY CITY</t>
-  </si>
-  <si>
-    <t>Name of School / School District :  MANAGOK CENTRAL SCHOOL/DISTRICT IX</t>
-  </si>
-  <si>
-    <t>School  ID Number:  126547</t>
-  </si>
-  <si>
-    <t>Last Mile School:  NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                            SBFP DepEd Focal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                School Head</t>
+    <t>Region X</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">                                              </t>
+      <t>Last Mile School:  ___Y   _</t>
     </r>
     <r>
       <rPr>
-        <b/>
         <u/>
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>DAVE M. FELICIANO</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">                     </t>
+      <t>/__</t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <u/>
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> RICKY S. BARCENA</t>
+      <t>N</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                            SBFP DepEd Focal</t>
+  </si>
+  <si>
+    <t>SBFP Form 2 (2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School  ID Number: </t>
+  </si>
+  <si>
+    <t>Nutritional Status at Start of Feeding</t>
+  </si>
+  <si>
+    <t>Date Feeding Started</t>
+  </si>
+  <si>
+    <t>SCHOOL-BASED FEEDING PROGRAM (SBFP) SUMMARY OF BENEFICIARIES &amp; START OF FEEDING (SY 2025-2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schools Division Office:  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">City/ Municipality/Barangay : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name of School / School District : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date of Start of Feeding: </t>
+  </si>
+  <si>
+    <t>Malaybalay City Division</t>
+  </si>
+  <si>
+    <t>Malaybalay City /</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -607,15 +503,48 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="8"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -626,13 +555,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <u/>
       <sz val="10"/>
@@ -640,28 +562,105 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="66">
+  <borders count="65">
     <border>
       <left/>
       <right/>
@@ -673,6 +672,19 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -715,212 +727,6 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -939,6 +745,321 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="hair">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="hair">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="hair">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -950,8 +1071,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
@@ -961,18 +1110,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right/>
@@ -982,112 +1120,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -1168,19 +1200,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -1316,64 +1335,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -1464,242 +1425,297 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="29"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="29" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="1"/>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="29" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="29" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="29" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{58BCC400-279A-462B-A174-642829BB1D6D}"/>
-    <cellStyle name="Normal 3" xfId="1" xr:uid="{7C38F9C8-5C77-4BEE-874A-68F49238C068}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1718,7 +1734,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
@@ -1726,10 +1742,10 @@
     <xdr:ext cx="752475" cy="409575"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image2.png" title="Image">
+        <xdr:cNvPr id="2" name="image1.png" title="Image">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABCC334E-E754-4C82-8B87-C0A14CB5A3AA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1742,6 +1758,10 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9267825" y="161925"/>
+          <a:ext cx="752475" cy="409575"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -1753,20 +1773,17 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>66675</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="647700" cy="533400"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="image1.png">
+        <xdr:cNvPr id="3" name="image2.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2972E51-39FA-4363-8CFC-98955E822101}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1780,7 +1797,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="209550"/>
+          <a:off x="66675" y="161925"/>
           <a:ext cx="647700" cy="533400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1791,47 +1808,128 @@
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="752475" cy="409575"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="image2.png" title="Image">
+        <xdr:cNvPr id="4" name="image2.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A0BEF44-3DD3-4A9F-A12E-0E733D3AB179}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{374CE6C4-55A7-4FA4-8AE2-2BF211437BE8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="10258425" y="161925"/>
-          <a:ext cx="752475" cy="409575"/>
+          <a:off x="69850" y="161925"/>
+          <a:ext cx="641350" cy="536575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5887A242-0A97-4EDD-901D-0D0E6D0C8FDF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="69850" y="161925"/>
+          <a:ext cx="641350" cy="536575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2032,1533 +2130,533 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:S1012"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2732F19A-0BB9-4697-A90A-A97E957C7075}">
+  <dimension ref="A1:Q994"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="7.54296875" customWidth="1"/>
-    <col min="3" max="5" width="8.54296875" customWidth="1"/>
-    <col min="6" max="6" width="9.36328125" customWidth="1"/>
-    <col min="7" max="10" width="8.54296875" customWidth="1"/>
-    <col min="11" max="11" width="9.36328125" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="7.08984375" customWidth="1"/>
-    <col min="14" max="14" width="6.90625" customWidth="1"/>
-    <col min="15" max="15" width="9.36328125" customWidth="1"/>
-    <col min="16" max="16" width="9.6328125" customWidth="1"/>
-    <col min="17" max="17" width="8.54296875" customWidth="1"/>
-    <col min="18" max="18" width="11.81640625" customWidth="1"/>
-    <col min="19" max="27" width="8" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" customWidth="1"/>
+    <col min="2" max="4" width="8.453125" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="16" width="8.453125" customWidth="1"/>
+    <col min="17" max="17" width="18.26953125" customWidth="1"/>
+    <col min="18" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
+    <row r="1" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="83"/>
+    </row>
+    <row r="3" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="84" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="83"/>
+    </row>
+    <row r="4" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="83"/>
+      <c r="O5" s="83"/>
+      <c r="P5" s="83"/>
+      <c r="Q5" s="83"/>
+    </row>
+    <row r="6" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="80" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+    </row>
+    <row r="7" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="80" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="79"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="76" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="77"/>
+    </row>
+    <row r="9" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="77" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="77"/>
+    </row>
+    <row r="10" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="76"/>
+      <c r="K10" s="76"/>
+    </row>
+    <row r="11" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="75"/>
+    </row>
+    <row r="12" spans="1:17" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="86" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="88" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="89"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="89"/>
+      <c r="H12" s="89"/>
+      <c r="I12" s="90"/>
+      <c r="J12" s="91" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="O12" s="95" t="s">
+        <v>10</v>
+      </c>
+      <c r="P12" s="94" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q12" s="96" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="87"/>
+      <c r="B13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13" s="87"/>
+      <c r="O13" s="87"/>
+      <c r="P13" s="87"/>
+      <c r="Q13" s="87"/>
+    </row>
+    <row r="14" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="61"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="62"/>
+      <c r="Q14" s="59"/>
+    </row>
+    <row r="15" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="61"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="64"/>
+      <c r="P15" s="62"/>
+      <c r="Q15" s="59"/>
+    </row>
+    <row r="16" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="61"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="64"/>
+      <c r="O16" s="64"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="59"/>
+    </row>
+    <row r="17" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="61"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="64"/>
+      <c r="O17" s="64"/>
+      <c r="P17" s="64"/>
+      <c r="Q17" s="59"/>
+    </row>
+    <row r="18" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="61"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="64"/>
+      <c r="P18" s="64"/>
+      <c r="Q18" s="59"/>
+    </row>
+    <row r="19" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="61"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="64"/>
+      <c r="O19" s="64"/>
+      <c r="P19" s="64"/>
+      <c r="Q19" s="59"/>
+    </row>
+    <row r="20" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="61"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="64"/>
+      <c r="O20" s="64"/>
+      <c r="P20" s="64"/>
+      <c r="Q20" s="59"/>
+    </row>
+    <row r="21" spans="1:17" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="67"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="71"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="59"/>
+    </row>
+    <row r="22" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-    </row>
-    <row r="2" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="96"/>
-      <c r="Q2" s="96"/>
-      <c r="R2" s="96"/>
-    </row>
-    <row r="3" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="84"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85"/>
-      <c r="K3" s="85"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="85"/>
-      <c r="N3" s="85"/>
-      <c r="O3" s="85"/>
-      <c r="P3" s="85"/>
-      <c r="Q3" s="85"/>
-      <c r="R3" s="85"/>
-    </row>
-    <row r="4" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="97" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="98"/>
-      <c r="K5" s="98"/>
-      <c r="L5" s="98"/>
-      <c r="M5" s="98"/>
-      <c r="N5" s="98"/>
-      <c r="O5" s="98"/>
-      <c r="P5" s="98"/>
-      <c r="Q5" s="98"/>
-      <c r="R5" s="98"/>
-    </row>
-    <row r="6" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="62" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-    </row>
-    <row r="7" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="62" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="62" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="62" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="B22" s="97"/>
+      <c r="C22" s="97"/>
+      <c r="D22" s="97"/>
+      <c r="J22" s="78" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="62" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="76" t="s">
+      <c r="K22" s="78"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="74"/>
+    </row>
+    <row r="23" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="98" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="99"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="J23" s="73"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="78" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="80"/>
-      <c r="K12" s="81" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="82"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="P12" s="94" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="R12" s="72" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="99.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="77"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O13" s="75"/>
-      <c r="P13" s="75"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="73"/>
-    </row>
-    <row r="14" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="93" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="8">
-        <v>0</v>
-      </c>
-      <c r="D14" s="8">
-        <v>8</v>
-      </c>
-      <c r="E14" s="8">
-        <v>59</v>
-      </c>
-      <c r="F14" s="8">
-        <v>3</v>
-      </c>
-      <c r="G14" s="8">
-        <v>1</v>
-      </c>
-      <c r="H14" s="8">
-        <v>1</v>
-      </c>
-      <c r="I14" s="8">
-        <v>37</v>
-      </c>
-      <c r="J14" s="8">
-        <v>31</v>
-      </c>
-      <c r="K14" s="8">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8">
-        <v>0</v>
-      </c>
-      <c r="M14" s="8">
-        <v>0</v>
-      </c>
-      <c r="N14" s="8">
-        <v>0</v>
-      </c>
-      <c r="O14" s="8">
-        <v>70</v>
-      </c>
-      <c r="P14" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="9"/>
-    </row>
-    <row r="15" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="91"/>
-      <c r="B15" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="8">
-        <v>0</v>
-      </c>
-      <c r="D15" s="8">
-        <v>3</v>
-      </c>
-      <c r="E15" s="8">
-        <v>52</v>
-      </c>
-      <c r="F15" s="8">
-        <v>1</v>
-      </c>
-      <c r="G15" s="8">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8">
-        <v>3</v>
-      </c>
-      <c r="I15" s="8">
-        <v>29</v>
-      </c>
-      <c r="J15" s="8">
-        <v>24</v>
-      </c>
-      <c r="K15" s="8">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8">
-        <v>0</v>
-      </c>
-      <c r="M15" s="8">
-        <v>0</v>
-      </c>
-      <c r="N15" s="8">
-        <v>0</v>
-      </c>
-      <c r="O15" s="8">
-        <v>56</v>
-      </c>
-      <c r="P15" s="8">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="9"/>
-    </row>
-    <row r="16" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="77"/>
-      <c r="B16" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="63">
-        <f>SUM(C14:C15)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="63">
-        <f t="shared" ref="D16:Q16" si="0">SUM(D14:D15)</f>
-        <v>11</v>
-      </c>
-      <c r="E16" s="63">
-        <f t="shared" si="0"/>
-        <v>111</v>
-      </c>
-      <c r="F16" s="63">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G16" s="63">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H16" s="63">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="I16" s="63">
-        <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-      <c r="J16" s="63">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="K16" s="63">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="63">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="63">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="63">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="63">
-        <f>SUM(O14:O15)</f>
-        <v>126</v>
-      </c>
-      <c r="P16" s="63">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Q16" s="63">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="64"/>
-      <c r="S16" s="59"/>
-    </row>
-    <row r="17" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="93" t="s">
+      <c r="M23" s="81"/>
+      <c r="N23" s="81"/>
+      <c r="O23" s="81"/>
+      <c r="P23" s="72"/>
+    </row>
+    <row r="24" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="8">
-        <v>8</v>
-      </c>
-      <c r="D17" s="8">
-        <v>6</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0</v>
-      </c>
-      <c r="F17" s="8">
-        <v>0</v>
-      </c>
-      <c r="G17" s="8">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8">
-        <v>0</v>
-      </c>
-      <c r="I17" s="8">
-        <v>11</v>
-      </c>
-      <c r="J17" s="8">
-        <v>3</v>
-      </c>
-      <c r="K17" s="8">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8">
-        <v>0</v>
-      </c>
-      <c r="M17" s="8">
-        <v>0</v>
-      </c>
-      <c r="N17" s="8">
-        <v>0</v>
-      </c>
-      <c r="O17" s="8">
-        <v>14</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>1</v>
-      </c>
-      <c r="R17" s="9"/>
-    </row>
-    <row r="18" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="91"/>
-      <c r="B18" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="8">
-        <v>5</v>
-      </c>
-      <c r="D18" s="8">
-        <v>4</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0</v>
-      </c>
-      <c r="F18" s="8">
-        <v>0</v>
-      </c>
-      <c r="G18" s="8">
-        <v>1</v>
-      </c>
-      <c r="H18" s="8">
-        <v>1</v>
-      </c>
-      <c r="I18" s="8">
-        <v>4</v>
-      </c>
-      <c r="J18" s="8">
-        <v>3</v>
-      </c>
-      <c r="K18" s="8">
-        <v>0</v>
-      </c>
-      <c r="L18" s="8">
-        <v>0</v>
-      </c>
-      <c r="M18" s="8">
-        <v>0</v>
-      </c>
-      <c r="N18" s="8">
-        <v>0</v>
-      </c>
-      <c r="O18" s="8">
-        <v>9</v>
-      </c>
-      <c r="P18" s="8">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>0</v>
-      </c>
-      <c r="R18" s="9"/>
-    </row>
-    <row r="19" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="77"/>
-      <c r="B19" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="63">
-        <f>SUM(C17:C18)</f>
-        <v>13</v>
-      </c>
-      <c r="D19" s="63">
-        <f t="shared" ref="D19" si="1">SUM(D17:D18)</f>
-        <v>10</v>
-      </c>
-      <c r="E19" s="63">
-        <f t="shared" ref="E19" si="2">SUM(E17:E18)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="63">
-        <f t="shared" ref="F19" si="3">SUM(F17:F18)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="63">
-        <f t="shared" ref="G19" si="4">SUM(G17:G18)</f>
-        <v>1</v>
-      </c>
-      <c r="H19" s="63">
-        <f t="shared" ref="H19" si="5">SUM(H17:H18)</f>
-        <v>1</v>
-      </c>
-      <c r="I19" s="63">
-        <f t="shared" ref="I19" si="6">SUM(I17:I18)</f>
-        <v>15</v>
-      </c>
-      <c r="J19" s="63">
-        <f t="shared" ref="J19" si="7">SUM(J17:J18)</f>
-        <v>6</v>
-      </c>
-      <c r="K19" s="63">
-        <f t="shared" ref="K19" si="8">SUM(K17:K18)</f>
-        <v>0</v>
-      </c>
-      <c r="L19" s="63">
-        <f t="shared" ref="L19" si="9">SUM(L17:L18)</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="63">
-        <f t="shared" ref="M19" si="10">SUM(M17:M18)</f>
-        <v>0</v>
-      </c>
-      <c r="N19" s="63">
-        <f t="shared" ref="N19" si="11">SUM(N17:N18)</f>
-        <v>0</v>
-      </c>
-      <c r="O19" s="63">
-        <f t="shared" ref="O19" si="12">SUM(O17:O18)</f>
-        <v>23</v>
-      </c>
-      <c r="P19" s="63">
-        <f t="shared" ref="P19" si="13">SUM(P17:P18)</f>
-        <v>3</v>
-      </c>
-      <c r="Q19" s="63">
-        <f t="shared" ref="Q19" si="14">SUM(Q17:Q18)</f>
-        <v>1</v>
-      </c>
-      <c r="R19" s="64"/>
-    </row>
-    <row r="20" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="93" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="8">
-        <v>3</v>
-      </c>
-      <c r="D20" s="8">
-        <v>7</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0</v>
-      </c>
-      <c r="F20" s="8">
-        <v>0</v>
-      </c>
-      <c r="G20" s="8">
-        <v>0</v>
-      </c>
-      <c r="H20" s="8">
-        <v>3</v>
-      </c>
-      <c r="I20" s="8">
-        <v>7</v>
-      </c>
-      <c r="J20" s="8">
-        <v>0</v>
-      </c>
-      <c r="K20" s="8">
-        <v>0</v>
-      </c>
-      <c r="L20" s="8">
-        <v>0</v>
-      </c>
-      <c r="M20" s="8">
-        <v>0</v>
-      </c>
-      <c r="N20" s="8">
-        <v>0</v>
-      </c>
-      <c r="O20" s="8">
-        <v>10</v>
-      </c>
-      <c r="P20" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>0</v>
-      </c>
-      <c r="R20" s="9"/>
-    </row>
-    <row r="21" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="91"/>
-      <c r="B21" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="8">
-        <v>2</v>
-      </c>
-      <c r="D21" s="8">
-        <v>3</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0</v>
-      </c>
-      <c r="F21" s="8">
-        <v>0</v>
-      </c>
-      <c r="G21" s="8">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8">
-        <v>1</v>
-      </c>
-      <c r="I21" s="8">
-        <v>4</v>
-      </c>
-      <c r="J21" s="8">
-        <v>0</v>
-      </c>
-      <c r="K21" s="8">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8">
-        <v>0</v>
-      </c>
-      <c r="M21" s="8">
-        <v>0</v>
-      </c>
-      <c r="N21" s="8">
-        <v>0</v>
-      </c>
-      <c r="O21" s="8">
-        <v>5</v>
-      </c>
-      <c r="P21" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>0</v>
-      </c>
-      <c r="R21" s="9"/>
-    </row>
-    <row r="22" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="77"/>
-      <c r="B22" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="63">
-        <f>SUM(C20:C21)</f>
-        <v>5</v>
-      </c>
-      <c r="D22" s="63">
-        <f t="shared" ref="D22" si="15">SUM(D20:D21)</f>
-        <v>10</v>
-      </c>
-      <c r="E22" s="63">
-        <f t="shared" ref="E22" si="16">SUM(E20:E21)</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="63">
-        <f t="shared" ref="F22" si="17">SUM(F20:F21)</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="63">
-        <f t="shared" ref="G22" si="18">SUM(G20:G21)</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="63">
-        <f t="shared" ref="H22" si="19">SUM(H20:H21)</f>
-        <v>4</v>
-      </c>
-      <c r="I22" s="63">
-        <f t="shared" ref="I22" si="20">SUM(I20:I21)</f>
-        <v>11</v>
-      </c>
-      <c r="J22" s="63">
-        <f t="shared" ref="J22" si="21">SUM(J20:J21)</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="63">
-        <f t="shared" ref="K22" si="22">SUM(K20:K21)</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="63">
-        <f t="shared" ref="L22" si="23">SUM(L20:L21)</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="63">
-        <f t="shared" ref="M22" si="24">SUM(M20:M21)</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="63">
-        <f t="shared" ref="N22" si="25">SUM(N20:N21)</f>
-        <v>0</v>
-      </c>
-      <c r="O22" s="63">
-        <f t="shared" ref="O22" si="26">SUM(O20:O21)</f>
-        <v>15</v>
-      </c>
-      <c r="P22" s="63">
-        <f t="shared" ref="P22" si="27">SUM(P20:P21)</f>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="63">
-        <f t="shared" ref="Q22" si="28">SUM(Q20:Q21)</f>
-        <v>0</v>
-      </c>
-      <c r="R22" s="60"/>
-    </row>
-    <row r="23" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="93" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="8">
-        <v>6</v>
-      </c>
-      <c r="D23" s="8">
-        <v>0</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0</v>
-      </c>
-      <c r="F23" s="8">
-        <v>0</v>
-      </c>
-      <c r="G23" s="8">
-        <v>0</v>
-      </c>
-      <c r="H23" s="8">
-        <v>0</v>
-      </c>
-      <c r="I23" s="8">
-        <v>4</v>
-      </c>
-      <c r="J23" s="8">
-        <v>2</v>
-      </c>
-      <c r="K23" s="8">
-        <v>0</v>
-      </c>
-      <c r="L23" s="8">
-        <v>0</v>
-      </c>
-      <c r="M23" s="8">
-        <v>0</v>
-      </c>
-      <c r="N23" s="8">
-        <v>0</v>
-      </c>
-      <c r="O23" s="8">
-        <v>6</v>
-      </c>
-      <c r="P23" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>0</v>
-      </c>
-      <c r="R23" s="9"/>
-    </row>
-    <row r="24" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="91"/>
-      <c r="B24" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="8">
-        <v>5</v>
-      </c>
-      <c r="D24" s="8">
-        <v>0</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0</v>
-      </c>
-      <c r="F24" s="8">
-        <v>0</v>
-      </c>
-      <c r="G24" s="8">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8">
-        <v>0</v>
-      </c>
-      <c r="I24" s="8">
-        <v>3</v>
-      </c>
-      <c r="J24" s="8">
-        <v>2</v>
-      </c>
-      <c r="K24" s="8">
-        <v>0</v>
-      </c>
-      <c r="L24" s="8">
-        <v>0</v>
-      </c>
-      <c r="M24" s="8">
-        <v>0</v>
-      </c>
-      <c r="N24" s="8">
-        <v>0</v>
-      </c>
-      <c r="O24" s="8">
-        <v>5</v>
-      </c>
-      <c r="P24" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>0</v>
-      </c>
-      <c r="R24" s="9"/>
-    </row>
-    <row r="25" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="77"/>
-      <c r="B25" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="63">
-        <f>SUM(C23:C24)</f>
-        <v>11</v>
-      </c>
-      <c r="D25" s="63">
-        <f t="shared" ref="D25" si="29">SUM(D23:D24)</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="63">
-        <f t="shared" ref="E25" si="30">SUM(E23:E24)</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="63">
-        <f t="shared" ref="F25" si="31">SUM(F23:F24)</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="63">
-        <f t="shared" ref="G25" si="32">SUM(G23:G24)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="63">
-        <f t="shared" ref="H25" si="33">SUM(H23:H24)</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="63">
-        <f t="shared" ref="I25" si="34">SUM(I23:I24)</f>
-        <v>7</v>
-      </c>
-      <c r="J25" s="63">
-        <f t="shared" ref="J25" si="35">SUM(J23:J24)</f>
-        <v>4</v>
-      </c>
-      <c r="K25" s="63">
-        <f t="shared" ref="K25" si="36">SUM(K23:K24)</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="63">
-        <f t="shared" ref="L25" si="37">SUM(L23:L24)</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="63">
-        <f t="shared" ref="M25" si="38">SUM(M23:M24)</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="63">
-        <f t="shared" ref="N25" si="39">SUM(N23:N24)</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="63">
-        <f t="shared" ref="O25" si="40">SUM(O23:O24)</f>
-        <v>11</v>
-      </c>
-      <c r="P25" s="63">
-        <f t="shared" ref="P25" si="41">SUM(P23:P24)</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="63">
-        <f t="shared" ref="Q25" si="42">SUM(Q23:Q24)</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="60"/>
-    </row>
-    <row r="26" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="93" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="9"/>
-    </row>
-    <row r="27" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="91"/>
-      <c r="B27" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="9"/>
-    </row>
-    <row r="28" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="77"/>
-      <c r="B28" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="8">
-        <f>SUM(C26:C27)</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="8">
-        <f t="shared" ref="D28" si="43">SUM(D26:D27)</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="8">
-        <f t="shared" ref="E28" si="44">SUM(E26:E27)</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="8">
-        <f t="shared" ref="F28" si="45">SUM(F26:F27)</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="8">
-        <f t="shared" ref="G28" si="46">SUM(G26:G27)</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="8">
-        <f t="shared" ref="H28" si="47">SUM(H26:H27)</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="8">
-        <f t="shared" ref="I28" si="48">SUM(I26:I27)</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="8">
-        <f t="shared" ref="J28" si="49">SUM(J26:J27)</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="8">
-        <f t="shared" ref="K28" si="50">SUM(K26:K27)</f>
-        <v>0</v>
-      </c>
-      <c r="L28" s="8">
-        <f t="shared" ref="L28" si="51">SUM(L26:L27)</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="8">
-        <f t="shared" ref="M28" si="52">SUM(M26:M27)</f>
-        <v>0</v>
-      </c>
-      <c r="N28" s="8">
-        <f t="shared" ref="N28" si="53">SUM(N26:N27)</f>
-        <v>0</v>
-      </c>
-      <c r="O28" s="8">
-        <f t="shared" ref="O28" si="54">SUM(O26:O27)</f>
-        <v>0</v>
-      </c>
-      <c r="P28" s="8">
-        <f t="shared" ref="P28" si="55">SUM(P26:P27)</f>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="8">
-        <f t="shared" ref="Q28" si="56">SUM(Q26:Q27)</f>
-        <v>0</v>
-      </c>
-      <c r="R28" s="60">
-        <f t="shared" ref="R28" si="57">SUM(R26:R27)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="93" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="9"/>
-    </row>
-    <row r="30" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="91"/>
-      <c r="B30" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="8"/>
-      <c r="R30" s="9"/>
-    </row>
-    <row r="31" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="77"/>
-      <c r="B31" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="8">
-        <f>SUM(C29:C30)</f>
-        <v>0</v>
-      </c>
-      <c r="D31" s="8">
-        <f t="shared" ref="D31" si="58">SUM(D29:D30)</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="8">
-        <f t="shared" ref="E31" si="59">SUM(E29:E30)</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="8">
-        <f t="shared" ref="F31" si="60">SUM(F29:F30)</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="8">
-        <f t="shared" ref="G31" si="61">SUM(G29:G30)</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="8">
-        <f t="shared" ref="H31" si="62">SUM(H29:H30)</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="8">
-        <f t="shared" ref="I31" si="63">SUM(I29:I30)</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="8">
-        <f t="shared" ref="J31" si="64">SUM(J29:J30)</f>
-        <v>0</v>
-      </c>
-      <c r="K31" s="8">
-        <f t="shared" ref="K31" si="65">SUM(K29:K30)</f>
-        <v>0</v>
-      </c>
-      <c r="L31" s="8">
-        <f t="shared" ref="L31" si="66">SUM(L29:L30)</f>
-        <v>0</v>
-      </c>
-      <c r="M31" s="8">
-        <f t="shared" ref="M31" si="67">SUM(M29:M30)</f>
-        <v>0</v>
-      </c>
-      <c r="N31" s="8">
-        <f t="shared" ref="N31" si="68">SUM(N29:N30)</f>
-        <v>0</v>
-      </c>
-      <c r="O31" s="8">
-        <f t="shared" ref="O31" si="69">SUM(O29:O30)</f>
-        <v>0</v>
-      </c>
-      <c r="P31" s="8">
-        <f t="shared" ref="P31" si="70">SUM(P29:P30)</f>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="8">
-        <f t="shared" ref="Q31" si="71">SUM(Q29:Q30)</f>
-        <v>0</v>
-      </c>
-      <c r="R31" s="60">
-        <f t="shared" ref="R31" si="72">SUM(R29:R30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="93" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-      <c r="P32" s="8"/>
-      <c r="Q32" s="8"/>
-      <c r="R32" s="9"/>
-    </row>
-    <row r="33" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="91"/>
-      <c r="B33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="9"/>
-    </row>
-    <row r="34" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="77"/>
-      <c r="B34" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="8">
-        <f>SUM(C32:C33)</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="8">
-        <f t="shared" ref="D34" si="73">SUM(D32:D33)</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="8">
-        <f t="shared" ref="E34" si="74">SUM(E32:E33)</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="8">
-        <f t="shared" ref="F34" si="75">SUM(F32:F33)</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="8">
-        <f t="shared" ref="G34" si="76">SUM(G32:G33)</f>
-        <v>0</v>
-      </c>
-      <c r="H34" s="8">
-        <f t="shared" ref="H34" si="77">SUM(H32:H33)</f>
-        <v>0</v>
-      </c>
-      <c r="I34" s="8">
-        <f t="shared" ref="I34" si="78">SUM(I32:I33)</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="8">
-        <f t="shared" ref="J34" si="79">SUM(J32:J33)</f>
-        <v>0</v>
-      </c>
-      <c r="K34" s="8">
-        <f t="shared" ref="K34" si="80">SUM(K32:K33)</f>
-        <v>0</v>
-      </c>
-      <c r="L34" s="8">
-        <f t="shared" ref="L34" si="81">SUM(L32:L33)</f>
-        <v>0</v>
-      </c>
-      <c r="M34" s="8">
-        <f t="shared" ref="M34" si="82">SUM(M32:M33)</f>
-        <v>0</v>
-      </c>
-      <c r="N34" s="8">
-        <f t="shared" ref="N34" si="83">SUM(N32:N33)</f>
-        <v>0</v>
-      </c>
-      <c r="O34" s="8">
-        <f t="shared" ref="O34" si="84">SUM(O32:O33)</f>
-        <v>0</v>
-      </c>
-      <c r="P34" s="8">
-        <f t="shared" ref="P34" si="85">SUM(P32:P33)</f>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="8">
-        <f t="shared" ref="Q34" si="86">SUM(Q32:Q33)</f>
-        <v>0</v>
-      </c>
-      <c r="R34" s="60">
-        <f t="shared" ref="R34" si="87">SUM(R32:R33)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="90" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8"/>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="9"/>
-    </row>
-    <row r="36" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="91"/>
-      <c r="B36" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="8"/>
-      <c r="P36" s="8"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="9"/>
-    </row>
-    <row r="37" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="92"/>
-      <c r="B37" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" s="13">
-        <f>SUM(C16,C19,C22,C25,C28,C31,C34,)</f>
-        <v>29</v>
-      </c>
-      <c r="D37" s="13">
-        <f t="shared" ref="D37:R37" si="88">SUM(D16,D19,D22,D25,D28,D31,D34,)</f>
-        <v>31</v>
-      </c>
-      <c r="E37" s="13">
-        <f t="shared" si="88"/>
-        <v>111</v>
-      </c>
-      <c r="F37" s="13">
-        <f t="shared" si="88"/>
-        <v>4</v>
-      </c>
-      <c r="G37" s="13">
-        <f t="shared" si="88"/>
-        <v>2</v>
-      </c>
-      <c r="H37" s="13">
-        <f t="shared" si="88"/>
-        <v>9</v>
-      </c>
-      <c r="I37" s="13">
-        <f t="shared" si="88"/>
-        <v>99</v>
-      </c>
-      <c r="J37" s="13">
-        <f t="shared" si="88"/>
-        <v>65</v>
-      </c>
-      <c r="K37" s="13">
-        <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="L37" s="13">
-        <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="M37" s="13">
-        <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="N37" s="13">
-        <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O37" s="13">
-        <f t="shared" si="88"/>
-        <v>175</v>
-      </c>
-      <c r="P37" s="13">
-        <f t="shared" si="88"/>
-        <v>8</v>
-      </c>
-      <c r="Q37" s="13">
-        <f t="shared" si="88"/>
-        <v>1</v>
-      </c>
-      <c r="R37" s="61">
-        <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="S37" s="59"/>
-    </row>
-    <row r="38" spans="1:19" s="68" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="65" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" s="65"/>
-      <c r="C38" s="65"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="69"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="69"/>
-      <c r="K38" s="65" t="s">
-        <v>2</v>
-      </c>
-      <c r="L38" s="65"/>
-      <c r="M38" s="65"/>
-      <c r="N38" s="65"/>
-      <c r="O38" s="65"/>
-      <c r="P38" s="65"/>
-    </row>
-    <row r="39" spans="1:19" s="68" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="65"/>
-      <c r="B39" s="65"/>
-      <c r="C39" s="65"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="65"/>
-      <c r="L39" s="65"/>
-      <c r="M39" s="65"/>
-      <c r="N39" s="65"/>
-      <c r="O39" s="65"/>
-      <c r="P39" s="65"/>
-    </row>
-    <row r="40" spans="1:19" s="68" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="66" t="s">
-        <v>82</v>
-      </c>
-      <c r="G40" s="69"/>
-      <c r="H40" s="69"/>
-      <c r="I40" s="69"/>
-      <c r="J40" s="69"/>
-      <c r="K40" s="70" t="s">
-        <v>83</v>
-      </c>
-      <c r="L40" s="71"/>
-      <c r="M40" s="71"/>
-      <c r="N40" s="71"/>
-      <c r="O40" s="71"/>
-      <c r="P40" s="71"/>
-      <c r="Q40" s="71"/>
-    </row>
-    <row r="41" spans="1:19" s="68" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="67" t="s">
-        <v>80</v>
-      </c>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="86" t="s">
-        <v>81</v>
-      </c>
-      <c r="L41" s="71"/>
-      <c r="M41" s="71"/>
-      <c r="N41" s="71"/>
-      <c r="O41" s="71"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="71"/>
-    </row>
-    <row r="42" spans="1:19" s="68" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="87" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42" s="85"/>
-      <c r="C42" s="85"/>
-      <c r="D42" s="85"/>
-      <c r="E42" s="85"/>
-      <c r="F42" s="85"/>
-      <c r="G42" s="85"/>
-      <c r="H42" s="85"/>
-      <c r="I42" s="85"/>
-      <c r="J42" s="85"/>
-      <c r="K42" s="88"/>
-      <c r="L42" s="88"/>
-      <c r="M42" s="88"/>
-      <c r="N42" s="88"/>
-      <c r="O42" s="88"/>
-      <c r="P42" s="88"/>
-      <c r="Q42" s="88"/>
-      <c r="R42" s="85"/>
-    </row>
-    <row r="43" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="85"/>
-      <c r="B43" s="85"/>
-      <c r="C43" s="85"/>
-      <c r="D43" s="85"/>
-      <c r="E43" s="85"/>
-      <c r="F43" s="85"/>
-      <c r="G43" s="85"/>
-      <c r="H43" s="85"/>
-      <c r="I43" s="85"/>
-      <c r="J43" s="85"/>
-      <c r="K43" s="85"/>
-      <c r="L43" s="85"/>
-      <c r="M43" s="85"/>
-      <c r="N43" s="85"/>
-      <c r="O43" s="85"/>
-      <c r="P43" s="85"/>
-      <c r="Q43" s="85"/>
-      <c r="R43" s="85"/>
-    </row>
-    <row r="44" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="83"/>
+      <c r="J24" s="83"/>
+      <c r="K24" s="83"/>
+      <c r="L24" s="83"/>
+      <c r="M24" s="83"/>
+      <c r="N24" s="83"/>
+      <c r="O24" s="83"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="83"/>
+    </row>
+    <row r="25" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="83"/>
+      <c r="B25" s="83"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="83"/>
+      <c r="J25" s="83"/>
+      <c r="K25" s="83"/>
+      <c r="L25" s="83"/>
+      <c r="M25" s="83"/>
+      <c r="N25" s="83"/>
+      <c r="O25" s="83"/>
+      <c r="P25" s="83"/>
+      <c r="Q25" s="83"/>
+    </row>
+    <row r="26" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4505,52 +3603,39 @@
     <row r="992" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="993" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="994" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1002" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1003" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1004" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1005" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1006" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1007" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1008" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1009" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1010" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1011" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1012" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="K41:Q41"/>
-    <mergeCell ref="A42:R43"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A29:A31"/>
+  <mergeCells count="28">
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="A24:Q25"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A5:Q5"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="O12:O13"/>
     <mergeCell ref="P12:P13"/>
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A3:R3"/>
-    <mergeCell ref="A5:R5"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="K40:Q40"/>
-    <mergeCell ref="R12:R13"/>
     <mergeCell ref="Q12:Q13"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="D7:K7"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="D10:K10"/>
+    <mergeCell ref="D9:K9"/>
+    <mergeCell ref="D8:K8"/>
+    <mergeCell ref="J22:K22"/>
   </mergeCells>
-  <pageMargins left="0.11811023622047245" right="3.937007874015748E-2" top="0.11811023622047245" bottom="0.11811023622047245" header="0.11811023622047245" footer="0.11811023622047245"/>
-  <pageSetup paperSize="14" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="75" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -4562,90 +3647,90 @@
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" customWidth="1"/>
+    <col min="3" max="3" width="14.7265625" customWidth="1"/>
     <col min="4" max="9" width="7" customWidth="1"/>
-    <col min="10" max="15" width="6.81640625" customWidth="1"/>
-    <col min="16" max="16" width="5.08984375" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="0.90625" hidden="1" customWidth="1"/>
+    <col min="10" max="15" width="6.7265625" customWidth="1"/>
+    <col min="16" max="16" width="5.1796875" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="0.81640625" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="17" customWidth="1"/>
     <col min="19" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="17"/>
+      <c r="A1" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="19"/>
     </row>
     <row r="2" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="95" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85"/>
-      <c r="K3" s="85"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="85"/>
-      <c r="N3" s="85"/>
-      <c r="O3" s="85"/>
-      <c r="P3" s="85"/>
-      <c r="Q3" s="85"/>
-      <c r="R3" s="85"/>
+      <c r="A3" s="101" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="83"/>
     </row>
     <row r="4" spans="1:18" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="100" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="85"/>
-      <c r="K5" s="85"/>
-      <c r="L5" s="85"/>
-      <c r="M5" s="85"/>
-      <c r="N5" s="85"/>
-      <c r="O5" s="85"/>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="85"/>
-      <c r="R5" s="85"/>
+      <c r="A5" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="83"/>
+      <c r="O5" s="83"/>
+      <c r="P5" s="83"/>
+      <c r="Q5" s="83"/>
+      <c r="R5" s="83"/>
     </row>
     <row r="6" spans="1:18" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="95"/>
-      <c r="B6" s="85"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="85"/>
-      <c r="K6" s="85"/>
-      <c r="L6" s="85"/>
-      <c r="M6" s="85"/>
-      <c r="N6" s="85"/>
-      <c r="O6" s="85"/>
-      <c r="P6" s="85"/>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
+      <c r="A6" s="101"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="83"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="83"/>
+      <c r="P6" s="83"/>
+      <c r="Q6" s="83"/>
+      <c r="R6" s="83"/>
     </row>
     <row r="7" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
-        <v>40</v>
+      <c r="A7" s="20" t="s">
+        <v>33</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
@@ -4666,108 +3751,108 @@
       <c r="R7" s="14"/>
     </row>
     <row r="8" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>41</v>
+      <c r="A8" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>42</v>
+      <c r="A9" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="103" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="104"/>
+      <c r="C11" s="109" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="115" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="116"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="116"/>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="116"/>
+      <c r="L11" s="116"/>
+      <c r="M11" s="116"/>
+      <c r="N11" s="116"/>
+      <c r="O11" s="117"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="113"/>
+      <c r="R11" s="114" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="105"/>
+      <c r="B12" s="106"/>
+      <c r="C12" s="110"/>
+      <c r="D12" s="115" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="116"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="116"/>
+      <c r="H12" s="116"/>
+      <c r="I12" s="117"/>
+      <c r="J12" s="115" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="116"/>
+      <c r="L12" s="116"/>
+      <c r="M12" s="116"/>
+      <c r="N12" s="116"/>
+      <c r="O12" s="117"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="110"/>
+    </row>
+    <row r="13" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="107"/>
+      <c r="B13" s="108"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="21" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="101" t="s">
+      <c r="E13" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="102"/>
-      <c r="C11" s="107" t="s">
+      <c r="F13" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="113" t="s">
+      <c r="G13" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="114"/>
-      <c r="F11" s="114"/>
-      <c r="G11" s="114"/>
-      <c r="H11" s="114"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="114"/>
-      <c r="K11" s="114"/>
-      <c r="L11" s="114"/>
-      <c r="M11" s="114"/>
-      <c r="N11" s="114"/>
-      <c r="O11" s="115"/>
-      <c r="P11" s="110"/>
-      <c r="Q11" s="111"/>
-      <c r="R11" s="112" t="s">
+      <c r="H13" s="23" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="103"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="113" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="114"/>
-      <c r="F12" s="114"/>
-      <c r="G12" s="114"/>
-      <c r="H12" s="114"/>
-      <c r="I12" s="115"/>
-      <c r="J12" s="113" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" s="114"/>
-      <c r="L12" s="114"/>
-      <c r="M12" s="114"/>
-      <c r="N12" s="114"/>
-      <c r="O12" s="115"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="108"/>
-    </row>
-    <row r="13" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="105"/>
-      <c r="B13" s="106"/>
-      <c r="C13" s="109"/>
-      <c r="D13" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>54</v>
       </c>
       <c r="I13" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M13" s="24" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N13" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="O13" s="24" t="s">
         <v>27</v>
@@ -4776,7 +3861,7 @@
       <c r="Q13" s="26">
         <v>11</v>
       </c>
-      <c r="R13" s="109"/>
+      <c r="R13" s="111"/>
     </row>
     <row r="14" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27">
@@ -4797,7 +3882,7 @@
       <c r="N14" s="31"/>
       <c r="O14" s="32"/>
       <c r="P14" s="30"/>
-      <c r="Q14" s="3"/>
+      <c r="Q14" s="2"/>
       <c r="R14" s="34"/>
     </row>
     <row r="15" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -4819,7 +3904,7 @@
       <c r="N15" s="39"/>
       <c r="O15" s="40"/>
       <c r="P15" s="38"/>
-      <c r="Q15" s="3"/>
+      <c r="Q15" s="2"/>
       <c r="R15" s="42"/>
     </row>
     <row r="16" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -4841,7 +3926,7 @@
       <c r="N16" s="39"/>
       <c r="O16" s="40"/>
       <c r="P16" s="38"/>
-      <c r="Q16" s="3"/>
+      <c r="Q16" s="2"/>
       <c r="R16" s="42"/>
     </row>
     <row r="17" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -4863,7 +3948,7 @@
       <c r="N17" s="39"/>
       <c r="O17" s="40"/>
       <c r="P17" s="38"/>
-      <c r="Q17" s="3"/>
+      <c r="Q17" s="2"/>
       <c r="R17" s="42"/>
     </row>
     <row r="18" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -4885,7 +3970,7 @@
       <c r="N18" s="39"/>
       <c r="O18" s="40"/>
       <c r="P18" s="38"/>
-      <c r="Q18" s="3"/>
+      <c r="Q18" s="2"/>
       <c r="R18" s="42"/>
     </row>
     <row r="19" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -4907,7 +3992,7 @@
       <c r="N19" s="39"/>
       <c r="O19" s="40"/>
       <c r="P19" s="38"/>
-      <c r="Q19" s="3"/>
+      <c r="Q19" s="2"/>
       <c r="R19" s="42"/>
     </row>
     <row r="20" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -4929,7 +4014,7 @@
       <c r="N20" s="39"/>
       <c r="O20" s="40"/>
       <c r="P20" s="38"/>
-      <c r="Q20" s="3"/>
+      <c r="Q20" s="2"/>
       <c r="R20" s="42"/>
     </row>
     <row r="21" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -4951,7 +4036,7 @@
       <c r="N21" s="39"/>
       <c r="O21" s="40"/>
       <c r="P21" s="38"/>
-      <c r="Q21" s="3"/>
+      <c r="Q21" s="2"/>
       <c r="R21" s="42"/>
     </row>
     <row r="22" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -4973,7 +4058,7 @@
       <c r="N22" s="39"/>
       <c r="O22" s="40"/>
       <c r="P22" s="38"/>
-      <c r="Q22" s="3"/>
+      <c r="Q22" s="2"/>
       <c r="R22" s="42"/>
     </row>
     <row r="23" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -4995,7 +4080,7 @@
       <c r="N23" s="39"/>
       <c r="O23" s="40"/>
       <c r="P23" s="38"/>
-      <c r="Q23" s="3"/>
+      <c r="Q23" s="2"/>
       <c r="R23" s="42"/>
     </row>
     <row r="24" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -5017,7 +4102,7 @@
       <c r="N24" s="39"/>
       <c r="O24" s="40"/>
       <c r="P24" s="38"/>
-      <c r="Q24" s="3"/>
+      <c r="Q24" s="2"/>
       <c r="R24" s="42"/>
     </row>
     <row r="25" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -5039,7 +4124,7 @@
       <c r="N25" s="39"/>
       <c r="O25" s="40"/>
       <c r="P25" s="38"/>
-      <c r="Q25" s="3"/>
+      <c r="Q25" s="2"/>
       <c r="R25" s="42"/>
     </row>
     <row r="26" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -5061,7 +4146,7 @@
       <c r="N26" s="39"/>
       <c r="O26" s="40"/>
       <c r="P26" s="38"/>
-      <c r="Q26" s="3"/>
+      <c r="Q26" s="2"/>
       <c r="R26" s="42"/>
     </row>
     <row r="27" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -5083,7 +4168,7 @@
       <c r="N27" s="39"/>
       <c r="O27" s="40"/>
       <c r="P27" s="38"/>
-      <c r="Q27" s="3"/>
+      <c r="Q27" s="2"/>
       <c r="R27" s="42"/>
     </row>
     <row r="28" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -5105,7 +4190,7 @@
       <c r="N28" s="39"/>
       <c r="O28" s="40"/>
       <c r="P28" s="38"/>
-      <c r="Q28" s="3"/>
+      <c r="Q28" s="2"/>
       <c r="R28" s="42"/>
     </row>
     <row r="29" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -5127,7 +4212,7 @@
       <c r="N29" s="39"/>
       <c r="O29" s="40"/>
       <c r="P29" s="38"/>
-      <c r="Q29" s="3"/>
+      <c r="Q29" s="2"/>
       <c r="R29" s="42"/>
     </row>
     <row r="30" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -5149,7 +4234,7 @@
       <c r="N30" s="39"/>
       <c r="O30" s="40"/>
       <c r="P30" s="38"/>
-      <c r="Q30" s="3"/>
+      <c r="Q30" s="2"/>
       <c r="R30" s="42"/>
     </row>
     <row r="31" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -5171,7 +4256,7 @@
       <c r="N31" s="39"/>
       <c r="O31" s="40"/>
       <c r="P31" s="38"/>
-      <c r="Q31" s="3"/>
+      <c r="Q31" s="2"/>
       <c r="R31" s="42"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -5193,7 +4278,7 @@
       <c r="N32" s="39"/>
       <c r="O32" s="40"/>
       <c r="P32" s="38"/>
-      <c r="Q32" s="3"/>
+      <c r="Q32" s="2"/>
       <c r="R32" s="42"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -5215,92 +4300,92 @@
       <c r="N33" s="39"/>
       <c r="O33" s="40"/>
       <c r="P33" s="38"/>
-      <c r="Q33" s="3"/>
+      <c r="Q33" s="2"/>
       <c r="R33" s="42"/>
     </row>
     <row r="34" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="116" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="117"/>
+      <c r="A34" s="118" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="119"/>
       <c r="C34" s="43"/>
-      <c r="D34" s="118" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" s="119"/>
-      <c r="F34" s="119"/>
-      <c r="G34" s="119"/>
-      <c r="H34" s="119"/>
-      <c r="I34" s="119"/>
-      <c r="J34" s="119"/>
-      <c r="K34" s="119"/>
-      <c r="L34" s="119"/>
-      <c r="M34" s="119"/>
-      <c r="N34" s="119"/>
-      <c r="O34" s="117"/>
+      <c r="D34" s="120" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="121"/>
+      <c r="F34" s="121"/>
+      <c r="G34" s="121"/>
+      <c r="H34" s="121"/>
+      <c r="I34" s="121"/>
+      <c r="J34" s="121"/>
+      <c r="K34" s="121"/>
+      <c r="L34" s="121"/>
+      <c r="M34" s="121"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="119"/>
       <c r="P34" s="44"/>
       <c r="Q34" s="45"/>
       <c r="R34" s="46"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>58</v>
+      <c r="A35" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="C35" s="1"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
     </row>
     <row r="36" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
+      <c r="A36" s="2"/>
       <c r="B36" s="47" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C36" s="48" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D36" s="49"/>
       <c r="E36" s="50"/>
       <c r="F36" s="51"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
     </row>
     <row r="37" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="52" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C37" s="53" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D37" s="15"/>
       <c r="E37" s="16"/>
     </row>
     <row r="38" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="52" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D38" s="15"/>
       <c r="E38" s="16"/>
@@ -5308,10 +4393,10 @@
     </row>
     <row r="39" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="52" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C39" s="53" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D39" s="15"/>
       <c r="E39" s="16"/>
@@ -5320,10 +4405,10 @@
     </row>
     <row r="40" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="52" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C40" s="53" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D40" s="15"/>
       <c r="E40" s="16"/>
@@ -5332,7 +4417,7 @@
     </row>
     <row r="41" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="55" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C41" s="56"/>
       <c r="D41" s="57"/>
@@ -5342,87 +4427,87 @@
     </row>
     <row r="42" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>69</v>
+        <v>4</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="3"/>
+      <c r="B43" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" s="54"/>
       <c r="E43" s="54"/>
       <c r="F43" s="54"/>
-      <c r="H43" s="99" t="s">
-        <v>71</v>
-      </c>
-      <c r="I43" s="85"/>
-      <c r="J43" s="85"/>
-      <c r="K43" s="85"/>
-      <c r="L43" s="85"/>
-      <c r="M43" s="85"/>
-      <c r="N43" s="85"/>
+      <c r="H43" s="100" t="s">
+        <v>64</v>
+      </c>
+      <c r="I43" s="83"/>
+      <c r="J43" s="83"/>
+      <c r="K43" s="83"/>
+      <c r="L43" s="83"/>
+      <c r="M43" s="83"/>
+      <c r="N43" s="83"/>
     </row>
     <row r="44" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="3"/>
-      <c r="H44" s="99" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="85"/>
-      <c r="J44" s="85"/>
-      <c r="K44" s="85"/>
-      <c r="L44" s="85"/>
-      <c r="M44" s="85"/>
-      <c r="N44" s="85"/>
+      <c r="B44" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="H44" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="I44" s="83"/>
+      <c r="J44" s="83"/>
+      <c r="K44" s="83"/>
+      <c r="L44" s="83"/>
+      <c r="M44" s="83"/>
+      <c r="N44" s="83"/>
     </row>
     <row r="45" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="87" t="s">
-        <v>73</v>
-      </c>
-      <c r="B46" s="85"/>
-      <c r="C46" s="85"/>
-      <c r="D46" s="85"/>
-      <c r="E46" s="85"/>
-      <c r="F46" s="85"/>
-      <c r="G46" s="85"/>
-      <c r="H46" s="85"/>
-      <c r="I46" s="85"/>
-      <c r="J46" s="85"/>
-      <c r="K46" s="85"/>
-      <c r="L46" s="85"/>
-      <c r="M46" s="85"/>
-      <c r="N46" s="85"/>
-      <c r="O46" s="85"/>
-      <c r="P46" s="85"/>
-      <c r="Q46" s="85"/>
-      <c r="R46" s="85"/>
+      <c r="A46" s="82" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="83"/>
+      <c r="C46" s="83"/>
+      <c r="D46" s="83"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="83"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="83"/>
+      <c r="I46" s="83"/>
+      <c r="J46" s="83"/>
+      <c r="K46" s="83"/>
+      <c r="L46" s="83"/>
+      <c r="M46" s="83"/>
+      <c r="N46" s="83"/>
+      <c r="O46" s="83"/>
+      <c r="P46" s="83"/>
+      <c r="Q46" s="83"/>
+      <c r="R46" s="83"/>
     </row>
     <row r="47" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="85"/>
-      <c r="B47" s="85"/>
-      <c r="C47" s="85"/>
-      <c r="D47" s="85"/>
-      <c r="E47" s="85"/>
-      <c r="F47" s="85"/>
-      <c r="G47" s="85"/>
-      <c r="H47" s="85"/>
-      <c r="I47" s="85"/>
-      <c r="J47" s="85"/>
-      <c r="K47" s="85"/>
-      <c r="L47" s="85"/>
-      <c r="M47" s="85"/>
-      <c r="N47" s="85"/>
-      <c r="O47" s="85"/>
-      <c r="P47" s="85"/>
-      <c r="Q47" s="85"/>
-      <c r="R47" s="85"/>
+      <c r="A47" s="83"/>
+      <c r="B47" s="83"/>
+      <c r="C47" s="83"/>
+      <c r="D47" s="83"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="83"/>
+      <c r="H47" s="83"/>
+      <c r="I47" s="83"/>
+      <c r="J47" s="83"/>
+      <c r="K47" s="83"/>
+      <c r="L47" s="83"/>
+      <c r="M47" s="83"/>
+      <c r="N47" s="83"/>
+      <c r="O47" s="83"/>
+      <c r="P47" s="83"/>
+      <c r="Q47" s="83"/>
+      <c r="R47" s="83"/>
     </row>
     <row r="48" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
